--- a/Config/Datas/GuideStepDatas/GuideSteps.xlsx
+++ b/Config/Datas/GuideStepDatas/GuideSteps.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\GuideStepDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A54802C-AF31-417C-9746-1766247035E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DFD632-66F7-4926-8885-BC9E86D7F0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
   <si>
     <t>stepID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,6 +68,87 @@
   </si>
   <si>
     <t>1_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stepName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>串签教程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选择串签</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GuideTargetType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>串签栏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哔哔哔哔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>简单对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击任意处</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1_3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>isConcerned</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初见1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初见2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哎呀，你就是那个新来的星际旅商？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2_2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初见3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">我是莫奇，这家店的房东~ </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>店铺我都给你准备好了
+租金嘛...看你经营情况再说咯！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -119,10 +200,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -404,10 +494,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" style="4" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -415,18 +509,26 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -439,45 +541,127 @@
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="28" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="E5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="28" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D7" s="1"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Config/Datas/GuideStepDatas/GuideSteps.xlsx
+++ b/Config/Datas/GuideStepDatas/GuideSteps.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\BBQ\Config\Datas\GuideStepDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DFD632-66F7-4926-8885-BC9E86D7F0E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6DEAAA-8238-4D21-8C98-676F2EF8318A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
